--- a/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
+++ b/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
@@ -1,45 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\land\AOCoLUPpUA\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF94B7C1-28EB-4AAB-A6C5-9A13131631C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="320" yWindow="320" windowWidth="18820" windowHeight="6560"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId2"/>
+    <sheet name="Indonesian Data" sheetId="2" r:id="rId2"/>
+    <sheet name="AOCoLUPpUA" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="C_to_CO2">'[1]Conversion Factors'!$A$4</definedName>
-  </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
   <si>
     <t>AOCoLUPpUA Annual Ongoing Cost of Land Use Policies per Unit Area</t>
   </si>
@@ -47,9 +24,286 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>Hypothetical Natural Forest Concession – applying sustainable forest management in line with international certification standards and payment of all official taxes and fees</t>
+  </si>
+  <si>
+    <t>Assumed harvestable area (ha)</t>
+  </si>
+  <si>
+    <t>Number of years cut over</t>
+  </si>
+  <si>
+    <t>Hectares harvested per year</t>
+  </si>
+  <si>
+    <t>Annual production (m3) - 20 m3/ha</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Cost/m3</t>
+  </si>
+  <si>
+    <t>(USD)</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>PLANNING COSTS</t>
+  </si>
+  <si>
+    <t>Block delineation</t>
+  </si>
+  <si>
+    <t>Pre-harvest inventory</t>
+  </si>
+  <si>
+    <t>Survey, road planning and construction</t>
+  </si>
+  <si>
+    <t>Amortisation of concession fee</t>
+  </si>
+  <si>
+    <t>Amortisation of forest inventory</t>
+  </si>
+  <si>
+    <t>Amortisation of concession boundary delineation</t>
+  </si>
+  <si>
+    <t>Amortisation of satellite imagery</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>REHABILITATION PLANTING</t>
+  </si>
+  <si>
+    <t>Seedling costs</t>
+  </si>
+  <si>
+    <t>Planting in logged areas, roadsides and bare soil</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>SILVICULTURAL TREATMENTS</t>
+  </si>
+  <si>
+    <t>Post harvest inventory</t>
+  </si>
+  <si>
+    <t>Plant maintenance</t>
+  </si>
+  <si>
+    <t>Reserve area maintenance</t>
+  </si>
+  <si>
+    <t>Permanent sample plots</t>
+  </si>
+  <si>
+    <t>General facilities</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>HARVESTING COSTS</t>
+  </si>
+  <si>
+    <t>Felling (on contract with equipment provided)</t>
+  </si>
+  <si>
+    <t>Skidding (on contract with equipment provided)</t>
+  </si>
+  <si>
+    <t>Rafting/Hauling (on contract with equipment provided)</t>
+  </si>
+  <si>
+    <t>Maintenance of facilities and equipment</t>
+  </si>
+  <si>
+    <t>Mechanics workshop</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
+  <si>
+    <t>Tug boat and pontoon costs</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>OFFICIAL TAXES AND FEES</t>
+  </si>
+  <si>
+    <t>Land and buildings tax</t>
+  </si>
+  <si>
+    <t>Vehicular and heavy equipment tax</t>
+  </si>
+  <si>
+    <t>Log grading tax</t>
+  </si>
+  <si>
+    <t>Local government fees and contributions</t>
+  </si>
+  <si>
+    <t>Rehabilitation Fund (DR)</t>
+  </si>
+  <si>
+    <t>Forest Resource Provision Tax (PSDH)</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>SOCIAL AND ENVIRONMENTAL COSTS</t>
+  </si>
+  <si>
+    <t>Community liaison</t>
+  </si>
+  <si>
+    <t>Community fees</t>
+  </si>
+  <si>
+    <t>Amortisation of Environmental Impact Assessment</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>PAYMENT TO CUSTOMARY LAND OWNERS</t>
+  </si>
+  <si>
+    <t>VIII</t>
+  </si>
+  <si>
+    <t>GENERAL DEPRECIATION COSTS</t>
+  </si>
+  <si>
+    <t>Of field generators, heavy equipment</t>
+  </si>
+  <si>
+    <t>Of roads and buildings</t>
+  </si>
+  <si>
+    <t>Of workshop and camp generator and equipment</t>
+  </si>
+  <si>
+    <t>IX</t>
+  </si>
+  <si>
+    <t>WAGES, BONUSES, ADMINISTRATION</t>
+  </si>
+  <si>
+    <t>Wages and bonus</t>
+  </si>
+  <si>
+    <t>Field camp consumables and associated costs</t>
+  </si>
+  <si>
+    <t>Head office and marketing costs</t>
+  </si>
+  <si>
+    <t>Forest protection and security</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>UNOFFICIAL COSTS</t>
+  </si>
+  <si>
+    <t>Forest service officials - honorarium, entertainment</t>
+  </si>
+  <si>
+    <t>Forest security and protection</t>
+  </si>
+  <si>
+    <t>NGOs - honorarium. Entertainment</t>
+  </si>
+  <si>
+    <t>Village officials</t>
+  </si>
+  <si>
+    <t>Local government</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Grand total - Production cost</t>
+  </si>
+  <si>
+    <t>https://www.newforests.com.au/wp-content/uploads/2014/08/200712-Carbon-FInance-for-REDD-at-the-Forest-Frontier.pdf</t>
+  </si>
+  <si>
+    <t>Page 35-36 (Appendix A)</t>
+  </si>
+  <si>
+    <t>Carbon Finance for Reduced Emissions from Deforestation &amp; Degradation at the Forest Frontier: Financial Analysis of Alternate Land Uses in the Amazon,
+Congo and Papua, Indonesia</t>
+  </si>
+  <si>
+    <t>Marisa Meizlish, Dan Spethmann, Michael Barbara</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
+    <t>acres/ha</t>
+  </si>
+  <si>
+    <t>m3/ha</t>
+  </si>
+  <si>
+    <t>(from this row of the table)</t>
+  </si>
+  <si>
+    <t>We do not have data for maintenance costs of restored peatlands.  We assume</t>
+  </si>
+  <si>
+    <t>the costs are the same as those for forests.</t>
+  </si>
+  <si>
+    <t>This variable is for the costs to maintain lands previously affected by one of the</t>
+  </si>
+  <si>
+    <t>land use policies (such as "Avoid Deforestation" or "Peatland Restoration") and</t>
+  </si>
+  <si>
+    <t>avoid emission of sequestered CO2.</t>
+  </si>
+  <si>
+    <t>This variable is NOT for use with the Improved Forest Management policy,</t>
+  </si>
+  <si>
+    <t>as that policy must be repeated every year in order to obtain carbon benefits</t>
+  </si>
+  <si>
+    <t>in that year.  Its cost is handled in the "Implementation Cost of Land Use</t>
+  </si>
+  <si>
+    <t>Policies per Unit Area" variable.</t>
+  </si>
+  <si>
+    <t>Indonesia Notes</t>
+  </si>
+  <si>
+    <t>Calculations</t>
+  </si>
+  <si>
+    <t>$ / acre</t>
+  </si>
+  <si>
     <t>forest set asides</t>
   </si>
   <si>
@@ -71,26 +325,34 @@
     <t>annual maintenance cost ($ / acre)</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on consultation with the organization American Forests, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">annual ongoing for land affected by these policy levers is a </t>
-  </si>
-  <si>
-    <t>small part of lifetime costs. For this reason, we do not attempt</t>
-  </si>
-  <si>
-    <t>to track these in the US model.</t>
+    <t>Include in Non-Harvested Forest</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Our data source breaks down the costs for sustainable management of</t>
+  </si>
+  <si>
+    <t>regularly harvested forest.  Only some of these line items apply to</t>
+  </si>
+  <si>
+    <t>forest that is not harvested.  We try to pick out these line items to estimate</t>
+  </si>
+  <si>
+    <t>the costs of maintaining forest without harvesting.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="3">
+    <numFmt numFmtId="168" formatCode="###0;###0"/>
+    <numFmt numFmtId="169" formatCode="###0.00;###0.00"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,35 +369,71 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -147,76 +445,105 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="dashed">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="4"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
-      <alignment wrapText="1"/>
+  </cellStyleXfs>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Body: normal cell" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Footnotes: top row" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Table title" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -224,68 +551,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="About"/>
-      <sheetName val="CO2 Aff &amp; Ref"/>
-      <sheetName val="VFC-PIIiCRfAaREY"/>
-      <sheetName val="Lost Value Aff &amp; Ref"/>
-      <sheetName val="VFC-LVpIIiCAbAaR"/>
-      <sheetName val="One Time Cost Aff &amp; Ref"/>
-      <sheetName val="VFC-OTCpIIiCAbAaR"/>
-      <sheetName val="Ongoing Cost Aff &amp; Ref"/>
-      <sheetName val="VFC-OCpMCAbAaR"/>
-      <sheetName val="CO2 Set Asides"/>
-      <sheetName val="VFC-PACRfFSA"/>
-      <sheetName val="Lost Value Set Asides"/>
-      <sheetName val="VFC-LVpMCAbFSA"/>
-      <sheetName val="CO2 Avoided Deforestation"/>
-      <sheetName val="VFC-PACRfAD"/>
-      <sheetName val="Lost Value Avoided Deforestatio"/>
-      <sheetName val="VFC-LVpMCAbAD"/>
-      <sheetName val="County Data"/>
-      <sheetName val="Forest Mgmt Costs"/>
-      <sheetName val="Conversion Factors"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19">
-        <row r="4">
-          <cell r="A4">
-            <v>3.6666666666666665</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -331,7 +598,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,26 +631,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -416,23 +666,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -608,59 +841,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.45" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:2" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:1" ht="14.45" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="11">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -668,67 +959,888 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3.90625" customWidth="1"/>
+    <col min="2" max="2" width="40.81640625" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" customWidth="1"/>
+    <col min="4" max="4" width="20.1796875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="F4" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="5"/>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>2.47105</v>
+      </c>
+      <c r="G6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="F8" s="12">
+        <f>D81*F5/F6</f>
+        <v>18.939317294267617</v>
+      </c>
+      <c r="G8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>5</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>7</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="B16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="9">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>2</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>1</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>2</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>3</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>4</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>5</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="9">
+        <v>0.08</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+      <c r="B29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="5"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>1</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="9">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>2</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>3</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>4</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="9">
+        <v>9.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>5</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="9">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>6</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="9">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>7</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="5"/>
+      <c r="B39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="9">
+        <v>41.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="5"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>1</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>2</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>3</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="9">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>4</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="9">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>6</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>7</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="5"/>
+      <c r="B48" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="9">
+        <v>26.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="5"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="5"/>
+      <c r="B51" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="9">
+        <v>4.3099999999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="5"/>
+      <c r="B52" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="5"/>
+      <c r="B53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="5"/>
+      <c r="B54" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="9">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="5"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="5"/>
+      <c r="B57" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+    </row>
+    <row r="59" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A59" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="5"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="8">
+        <v>1</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="9">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="8">
+        <v>2</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="8">
+        <v>3</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="9">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="5"/>
+      <c r="B63" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="9">
+        <v>9.3800000000000008</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="8">
+        <v>1</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="8">
+        <v>2</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="8">
+        <v>3</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="8">
+        <v>4</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="5"/>
+      <c r="B70" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="9">
+        <v>11.12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="5"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="5"/>
+      <c r="B73" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="9">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="5"/>
+      <c r="B74" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" s="9">
+        <v>1.96</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="5"/>
+      <c r="B75" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C75" s="9">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="5"/>
+      <c r="B76" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="5"/>
+      <c r="B77" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="9">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="5"/>
+      <c r="B78" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="5"/>
+      <c r="B79" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C79" s="9">
+        <v>15.36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="5"/>
+      <c r="B81" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="9">
+        <v>120.73</v>
+      </c>
+      <c r="D81" s="14">
+        <f>SUMIFS(C8:C79,D8:D79,"yes")</f>
+        <v>2.34</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="B2" s="13">
+        <f>'Indonesian Data'!$F$8</f>
+        <v>18.939317294267617</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="B3" s="13">
+        <f>'Indonesian Data'!$F$8</f>
+        <v>18.939317294267617</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
+        <v>97</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="B5" s="13">
+        <f>'Indonesian Data'!$F$8</f>
+        <v>18.939317294267617</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
+        <v>99</v>
+      </c>
+      <c r="B6" s="13">
+        <f>'Indonesian Data'!$F$8</f>
+        <v>18.939317294267617</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="B7" s="13">
+        <f>'Indonesian Data'!$F$8</f>
+        <v>18.939317294267617</v>
       </c>
     </row>
   </sheetData>
